--- a/template/GeoDataTemplate -多边形.xlsx
+++ b/template/GeoDataTemplate -多边形.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="多边形" sheetId="3" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">多边形!$A$1:$B$20</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,144 +30,120 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>名称</t>
   </si>
   <si>
-    <t>WKT</t>
+    <t>polygon</t>
+  </si>
+  <si>
+    <t>高新区</t>
+  </si>
+  <si>
+    <t>114.655926 23.606362,114.655537 23.606362,114.655537 23.605466,114.655343 23.605288,114.655343 23.604930,114.655730 23.604929,114.656119 23.605286,114.656119 23.606182,114.655926 23.606362</t>
   </si>
   <si>
     <t>明珠</t>
   </si>
   <si>
-    <t>POLYGON ((114.652216 23.645610, 114.652022 23.645609, 114.651828 23.645430, 114.651828 23.645251, 114.651442 23.644891, 114.651442 23.644712, 114.652217 23.644714, 114.652411 23.644893, 114.652993 23.644893, 114.653186 23.645073, 114.653186 23.645252, 114.652604 23.645252, 114.652216 23.645610))</t>
+    <t>114.652216 23.645610,114.652022 23.645609,114.651828 23.645430,114.651828 23.645251,114.651442 23.644891,114.651442 23.644712,114.652217 23.644714,114.652411 23.644893,114.652993 23.644893,114.653186 23.645073,114.653186 23.645252,114.652604 23.645252,114.652216 23.645610</t>
   </si>
   <si>
     <t>埔前</t>
   </si>
   <si>
-    <t>POLYGON ((114.633644 23.595983, 114.633450 23.595980, 114.633449 23.595622, 114.634030 23.595093, 114.634030 23.594735, 114.634223 23.594558, 114.634416 23.594560, 114.634803 23.594925, 114.634804 23.595104, 114.634610 23.595101, 114.634417 23.595278, 114.634417 23.595457, 114.634224 23.595454, 114.633644 23.595983))</t>
+    <t>114.633644 23.595983,114.633450 23.595980,114.633449 23.595622,114.634030 23.595093,114.634030 23.594735,114.634223 23.594558,114.634416 23.594560,114.634803 23.594925,114.634804 23.595104,114.634610 23.595101,114.634417 23.595278,114.634417 23.595457,114.634224 23.595454,114.633644 23.595983</t>
   </si>
   <si>
     <t>佗城</t>
   </si>
   <si>
-    <t>POLYGON ((115.220320 24.082979, 115.219933 24.082972, 115.219739 24.082790, 115.218964 24.082775, 115.218769 24.082592, 115.218381 24.082585, 115.218381 24.082406, 115.218576 24.082230, 115.218576 24.082051, 115.218381 24.081868, 115.218381 24.081688, 115.218769 24.081337, 115.218769 24.081158, 115.218381 24.080792, 115.218381 24.080613, 115.218768 24.080620, 115.218769 24.080799, 115.218963 24.080983, 115.219933 24.081000, 115.219933 24.081358, 115.220126 24.081541, 115.220320 24.081366, 115.220319 24.080827, 115.220902 24.080838, 115.220902 24.082273, 115.220708 24.082448, 115.220320 24.082441, 115.220127 24.082617, 115.220320 24.082800, 115.220320 24.082979))</t>
+    <t>115.220320 24.082979,115.219933 24.082972,115.219739 24.082790,115.218964 24.082775,115.218769 24.082592,115.218381 24.082585,115.218381 24.082406,115.218576 24.082230,115.218576 24.082051,115.218381 24.081868,115.218381 24.081688,115.218769 24.081337,115.218769 24.081158,115.218381 24.080792,115.218381 24.080613,115.218768 24.080620,115.218769 24.080799,115.218963 24.080983,115.219933 24.081000,115.219933 24.081358,115.220126 24.081541,115.220320 24.081366,115.220319 24.080827,115.220902 24.080838,115.220902 24.082273,115.220708 24.082448,115.220320 24.082441,115.220127 24.082617,115.220320 24.082800,115.220320 24.082979</t>
   </si>
   <si>
     <t>蓝口</t>
   </si>
   <si>
-    <t>POLYGON ((115.113972 23.981231, 115.113584 23.981224, 115.113584 23.981045, 115.113778 23.980870, 115.113778 23.980691, 115.113972 23.980514, 115.113779 23.980331, 115.113779 23.980152, 115.113972 23.979977, 115.113972 23.979798, 115.113779 23.979614, 115.113779 23.978898, 115.113391 23.978532, 115.113197 23.978529, 115.113197 23.977992, 115.113392 23.977815, 115.113197 23.977633, 115.113197 23.977453, 115.113392 23.977457, 115.113780 23.977822, 115.113779 23.978360, 115.113973 23.978542, 115.113972 23.979438, 115.114166 23.979621, 115.114360 23.979624, 115.114748 23.979990, 115.114748 23.980169, 115.114554 23.980166, 115.114360 23.979983, 115.114166 23.980159, 115.114165 23.980697, 115.113972 23.980873, 115.113972 23.981231))</t>
+    <t>115.113972 23.981231,115.113584 23.981224,115.113584 23.981045,115.113778 23.980870,115.113778 23.980691,115.113972 23.980514,115.113779 23.980331,115.113779 23.980152,115.113972 23.979977,115.113972 23.979798,115.113779 23.979614,115.113779 23.978898,115.113391 23.978532,115.113197 23.978529,115.113197 23.977992,115.113392 23.977815,115.113197 23.977633,115.113197 23.977453,115.113392 23.977457,115.113780 23.977822,115.113779 23.978360,115.113973 23.978542,115.113972 23.979438,115.114166 23.979621,115.114360 23.979624,115.114748 23.979990,115.114748 23.980169,115.114554 23.980166,115.114360 23.979983,115.114166 23.980159,115.114165 23.980697,115.113972 23.980873,115.113972 23.981231</t>
   </si>
   <si>
     <t>龙窝</t>
   </si>
   <si>
-    <t>POLYGON ((115.288946 23.477664, 115.288360 23.477676, 115.288166 23.477500, 115.287776 23.477508, 115.287386 23.477157, 115.287192 23.477161, 115.287192 23.476982, 115.287581 23.476975, 115.287776 23.477150, 115.287971 23.476967, 115.287971 23.476787, 115.288165 23.476604, 115.288555 23.476597, 115.288556 23.477135, 115.288946 23.477485, 115.288946 23.477664))</t>
+    <t>115.288946 23.477664,115.288360 23.477676,115.288166 23.477500,115.287776 23.477508,115.287386 23.477157,115.287192 23.477161,115.287192 23.476982,115.287581 23.476975,115.287776 23.477150,115.287971 23.476967,115.287971 23.476787,115.288165 23.476604,115.288555 23.476597,115.288556 23.477135,115.288946 23.477485,115.288946 23.477664</t>
   </si>
   <si>
     <t>柏埔</t>
   </si>
   <si>
-    <t>POLYGON ((114.849100 23.714930, 114.848712 23.714925, 114.848518 23.714743, 114.848517 23.714026, 114.848322 23.713844, 114.848128 23.713842, 114.848128 23.713663, 114.848322 23.713486, 114.848517 23.713489, 114.849100 23.714034, 114.849294 23.714036, 114.849294 23.714215, 114.849489 23.714398, 114.849489 23.714577, 114.849294 23.714575, 114.849100 23.714751, 114.849100 23.714930))</t>
+    <t>114.849100 23.714930,114.848712 23.714925,114.848518 23.714743,114.848517 23.714026,114.848322 23.713844,114.848128 23.713842,114.848128 23.713663,114.848322 23.713486,114.848517 23.713489,114.849100 23.714034,114.849294 23.714036,114.849294 23.714215,114.849489 23.714398,114.849489 23.714577,114.849294 23.714575,114.849100 23.714751,114.849100 23.714930</t>
   </si>
   <si>
     <t>元善</t>
   </si>
   <si>
-    <t>POLYGON ((114.514455 24.403458, 114.514261 24.403454, 114.514261 24.403275, 114.513872 24.402909, 114.513872 24.402551, 114.513677 24.402368, 114.513483 24.402364, 114.513289 24.402181, 114.513289 24.402001, 114.513094 24.401818, 114.513094 24.401101, 114.513289 24.401105, 114.513289 24.401285, 114.513483 24.401468, 114.513483 24.401647, 114.513872 24.402012, 114.513872 24.402192, 114.514066 24.402375, 114.514066 24.402554, 114.514261 24.402737, 114.514261 24.402916, 114.514455 24.403100, 114.514455 24.403458))</t>
+    <t>114.514455 24.403458,114.514261 24.403454,114.514261 24.403275,114.513872 24.402909,114.513872 24.402551,114.513677 24.402368,114.513483 24.402364,114.513289 24.402181,114.513289 24.402001,114.513094 24.401818,114.513094 24.401101,114.513289 24.401105,114.513289 24.401285,114.513483 24.401468,114.513483 24.401647,114.513872 24.402012,114.513872 24.402192,114.514066 24.402375,114.514066 24.402554,114.514261 24.402737,114.514261 24.402916,114.514455 24.403100,114.514455 24.403458</t>
   </si>
   <si>
     <t>船塘</t>
   </si>
   <si>
-    <t>POLYGON ((114.851774 24.178369, 114.851191 24.178360, 114.851191 24.178002, 114.851386 24.178005, 114.851579 24.177829, 114.851774 24.177832, 114.851968 24.178014, 114.852356 24.178020, 114.852550 24.177844, 114.852550 24.177664, 114.852938 24.177670, 114.853132 24.177494, 114.853520 24.177500, 114.853520 24.177859, 114.852938 24.177850, 114.852550 24.178202, 114.851968 24.178193, 114.851774 24.178369))</t>
-  </si>
-  <si>
-    <t>POLYGON ((115.088391 23.958033, 115.088004 23.958029, 115.088003 23.957670, 115.088198 23.957493, 115.088198 23.957314, 115.088585 23.956960, 115.088972 23.956964, 115.089167 23.957146, 115.089167 23.957504, 115.088972 23.957502, 115.088779 23.957320, 115.088586 23.957497, 115.088586 23.957676, 115.088391 23.957854, 115.088391 23.958033))</t>
+    <t>114.851774 24.178369,114.851191 24.178360,114.851191 24.178002,114.851386 24.178005,114.851579 24.177829,114.851774 24.177832,114.851968 24.178014,114.852356 24.178020,114.852550 24.177844,114.852550 24.177664,114.852938 24.177670,114.853132 24.177494,114.853520 24.177500,114.853520 24.177859,114.852938 24.177850,114.852550 24.178202,114.851968 24.178193,114.851774 24.178369</t>
+  </si>
+  <si>
+    <t>115.088391 23.958033,115.088004 23.958029,115.088003 23.957670,115.088198 23.957493,115.088198 23.957314,115.088585 23.956960,115.088972 23.956964,115.089167 23.957146,115.089167 23.957504,115.088972 23.957502,115.088779 23.957320,115.088586 23.957497,115.088586 23.957676,115.088391 23.957854,115.088391 23.958033</t>
   </si>
   <si>
     <t>城西开发区</t>
   </si>
   <si>
-    <t>POLYGON ((115.161676 23.663558, 115.161481 23.663561, 115.161481 23.663382, 115.161676 23.663199, 115.161481 23.663023, 115.161482 23.662127, 115.161872 23.661762, 115.162068 23.661759, 115.162068 23.661938, 115.161677 23.662303, 115.161872 23.662480, 115.161871 23.663376, 115.161676 23.663558))</t>
+    <t>115.161676 23.663558,115.161481 23.663561,115.161481 23.663382,115.161676 23.663199,115.161481 23.663023,115.161482 23.662127,115.161872 23.661762,115.162068 23.661759,115.162068 23.661938,115.161677 23.662303,115.161872 23.662480,115.161871 23.663376,115.161676 23.663558</t>
   </si>
   <si>
     <t>骆湖</t>
   </si>
   <si>
-    <t>POLYGON ((114.875434 24.045596, 114.874853 24.045586, 114.874852 24.045406, 114.874659 24.045224, 114.874464 24.045220, 114.874464 24.045041, 114.874659 24.044866, 114.874658 24.044506, 114.874852 24.044510, 114.875240 24.044158, 114.875240 24.043800, 114.875628 24.043806, 114.875628 24.044343, 114.875434 24.044519, 114.875434 24.044879, 114.875628 24.045061, 114.875628 24.045240, 114.875434 24.045416, 114.875434 24.045596))</t>
+    <t>114.875434 24.045596,114.874853 24.045586,114.874852 24.045406,114.874659 24.045224,114.874464 24.045220,114.874464 24.045041,114.874659 24.044866,114.874658 24.044506,114.874852 24.044510,114.875240 24.044158,114.875240 24.043800,114.875628 24.043806,114.875628 24.044343,114.875434 24.044519,114.875434 24.044879,114.875628 24.045061,114.875628 24.045240,114.875434 24.045416,114.875434 24.045596</t>
   </si>
   <si>
     <t>城区</t>
   </si>
   <si>
-    <t>POLYGON ((114.741391 23.820378, 114.741196 23.820375, 114.741195 23.819299, 114.741390 23.819302, 114.741583 23.819126, 114.741777 23.819129, 114.741970 23.819313, 114.742163 23.819136, 114.742358 23.819139, 114.742358 23.819499, 114.741777 23.819488, 114.741583 23.819664, 114.741584 23.820202, 114.741391 23.820378))</t>
+    <t>114.741391 23.820378,114.741196 23.820375,114.741195 23.819299,114.741390 23.819302,114.741583 23.819126,114.741777 23.819129,114.741970 23.819313,114.742163 23.819136,114.742358 23.819139,114.742358 23.819499,114.741777 23.819488,114.741583 23.819664,114.741584 23.820202,114.741391 23.820378</t>
   </si>
   <si>
     <t>赤光</t>
   </si>
   <si>
-    <t>POLYGON ((115.432632 24.384807, 115.432436 24.384807, 115.432242 24.384628, 115.432242 24.383911, 115.432047 24.383732, 115.431658 24.383733, 115.431658 24.383195, 115.431853 24.383195, 115.432047 24.383373, 115.432437 24.383373, 115.432437 24.383732, 115.432632 24.383911, 115.432827 24.383911, 115.433216 24.384269, 115.433216 24.384449, 115.433021 24.384449, 115.432632 24.384807))</t>
+    <t>115.432632 24.384807,115.432436 24.384807,115.432242 24.384628,115.432242 24.383911,115.432047 24.383732,115.431658 24.383733,115.431658 24.383195,115.431853 24.383195,115.432047 24.383373,115.432437 24.383373,115.432437 24.383732,115.432632 24.383911,115.432827 24.383911,115.433216 24.384269,115.433216 24.384449,115.433021 24.384449,115.432632 24.384807</t>
   </si>
   <si>
     <t>三角</t>
   </si>
   <si>
-    <t>POLYGON ((114.799521 24.229161, 114.799131 24.229167, 114.799131 24.228987, 114.799326 24.228805, 114.799326 24.228626, 114.799521 24.228623, 114.800109 24.228076, 114.800109 24.227897, 114.799718 24.227545, 114.799718 24.227366, 114.799913 24.227363, 114.800109 24.227539, 114.800304 24.227536, 114.800499 24.227712, 114.800499 24.227891, 114.800304 24.228073, 114.800304 24.228253, 114.800499 24.228429, 114.800499 24.228608, 114.800108 24.228972, 114.799717 24.228978, 114.799521 24.229161))</t>
-  </si>
-  <si>
-    <t>POLYGON ((114.770081 24.199056, 114.769692 24.199054, 114.769691 24.198875, 114.769497 24.198694, 114.769302 24.198692, 114.769302 24.198155, 114.769497 24.198156, 114.769691 24.197978, 114.769886 24.197980, 114.769886 24.198159, 114.769691 24.198337, 114.770080 24.198697, 114.770081 24.199056))</t>
+    <t>114.799521 24.229161,114.799131 24.229167,114.799131 24.228987,114.799326 24.228805,114.799326 24.228626,114.799521 24.228623,114.800109 24.228076,114.800109 24.227897,114.799718 24.227545,114.799718 24.227366,114.799913 24.227363,114.800109 24.227539,114.800304 24.227536,114.800499 24.227712,114.800499 24.227891,114.800304 24.228073,114.800304 24.228253,114.800499 24.228429,114.800499 24.228608,114.800108 24.228972,114.799717 24.228978,114.799521 24.229161</t>
+  </si>
+  <si>
+    <t>114.770081 24.199056,114.769692 24.199054,114.769691 24.198875,114.769497 24.198694,114.769302 24.198692,114.769302 24.198155,114.769497 24.198156,114.769691 24.197978,114.769886 24.197980,114.769886 24.198159,114.769691 24.198337,114.770080 24.198697,114.770081 24.199056</t>
   </si>
   <si>
     <t>龙母</t>
   </si>
   <si>
-    <t>POLYGON ((115.393225 24.264146, 115.392835 24.264152, 115.392641 24.263976, 115.392641 24.263796, 115.392445 24.263619, 115.392445 24.263261, 115.392251 24.263085, 115.392251 24.262547, 115.392446 24.262544, 115.392446 24.262723, 115.392836 24.263077, 115.392836 24.263256, 115.393030 24.263432, 115.393030 24.263790, 115.393225 24.263967, 115.393225 24.264146))</t>
+    <t>115.393225 24.264146,115.392835 24.264152,115.392641 24.263976,115.392641 24.263796,115.392445 24.263619,115.392445 24.263261,115.392251 24.263085,115.392251 24.262547,115.392446 24.262544,115.392446 24.262723,115.392836 24.263077,115.392836 24.263256,115.393030 24.263432,115.393030 24.263790,115.393225 24.263967,115.393225 24.264146</t>
   </si>
   <si>
     <t>火车站</t>
   </si>
   <si>
-    <t>POLYGON ((114.676133 23.725686, 114.675355 23.725699, 114.675354 23.725161, 114.675744 23.724796, 114.675744 23.724617, 114.675938 23.724614, 114.675938 23.724793, 114.676328 23.725144, 114.676328 23.725503, 114.676133 23.725686))</t>
+    <t>114.676133 23.725686,114.675355 23.725699,114.675354 23.725161,114.675744 23.724796,114.675744 23.724617,114.675938 23.724614,114.675938 23.724793,114.676328 23.725144,114.676328 23.725503,114.676133 23.725686</t>
   </si>
   <si>
     <t>临江</t>
   </si>
   <si>
-    <t>POLYGON ((114.700470 23.631499, 114.700276 23.631502, 114.700082 23.631326, 114.699303 23.631337, 114.699109 23.631161, 114.698914 23.631343, 114.698720 23.631346, 114.698525 23.631170, 114.698136 23.631176, 114.698136 23.630997, 114.699693 23.630973, 114.699887 23.630790, 114.700083 23.630788, 114.700277 23.630965, 114.700277 23.631144, 114.700471 23.631320, 114.700470 23.631499))</t>
-  </si>
-  <si>
-    <t>顺天</t>
-  </si>
-  <si>
-    <t>POLYGON ((114.770670 24.106734, 114.770476 24.106733, 114.770476 24.106554, 114.770281 24.106373, 114.770282 24.106194, 114.770477 24.106195, 114.770671 24.106017, 114.770671 24.105838, 114.770866 24.105839, 114.771254 24.106199, 114.771254 24.106378, 114.771059 24.106557, 114.770865 24.106556, 114.770670 24.106734))</t>
-  </si>
-  <si>
-    <t>POLYGON ((114.878732 24.047081, 114.878539 24.047078, 114.878344 24.046896, 114.878151 24.046893, 114.877957 24.047070, 114.877762 24.047067, 114.877374 24.046703, 114.877374 24.046523, 114.877762 24.046529, 114.877957 24.046352, 114.877957 24.046173, 114.878150 24.046176, 114.878150 24.046355, 114.878344 24.046538, 114.878538 24.046541, 114.878539 24.046720, 114.878732 24.046902, 114.878732 24.047081))</t>
-  </si>
-  <si>
-    <t>POLYGON ((114.785856 24.202082, 114.785271 24.202087, 114.785271 24.201728, 114.785466 24.201727, 114.785661 24.201546, 114.785661 24.201366, 114.785855 24.201185, 114.786051 24.201184, 114.786636 24.201717, 114.786636 24.201896, 114.786442 24.201898, 114.786246 24.201721, 114.786051 24.201722, 114.785856 24.201903, 114.785856 24.202082))</t>
-  </si>
-  <si>
-    <t>上莞</t>
-  </si>
-  <si>
-    <t>POLYGON ((114.989602 24.101640, 114.989022 24.101632, 114.989022 24.101453, 114.988829 24.101271, 114.987864 24.101256, 114.987672 24.101433, 114.987478 24.101430, 114.987286 24.101248, 114.987092 24.101245, 114.987092 24.101066, 114.987286 24.101069, 114.987478 24.100892, 114.987865 24.100898, 114.988057 24.100721, 114.988057 24.100542, 114.988444 24.100190, 114.988830 24.100195, 114.989022 24.100377, 114.989216 24.100380, 114.989409 24.100562, 114.989409 24.100741, 114.989216 24.100738, 114.989022 24.100916, 114.989602 24.101461, 114.989602 24.101640))</t>
-  </si>
-  <si>
-    <t>灯塔</t>
-  </si>
-  <si>
-    <t>POLYGON ((114.854485 24.034990, 114.854292 24.034987, 114.853515 24.034257, 114.853515 24.034078, 114.853321 24.033895, 114.853321 24.033716, 114.852933 24.033351, 114.852933 24.033172, 114.853321 24.033178, 114.853515 24.033360, 114.853515 24.033720, 114.853710 24.033902, 114.853710 24.034081, 114.854292 24.034629, 114.854485 24.034632, 114.854485 24.034990))</t>
-  </si>
-  <si>
-    <t>苏区</t>
-  </si>
-  <si>
-    <t>POLYGON ((115.344238 23.359721, 115.344044 23.359718, 115.344043 23.358284, 115.344237 23.358287, 115.344430 23.358111, 115.344623 23.358115, 115.344623 23.358653, 115.344238 23.359004, 115.344431 23.359186, 115.344431 23.359365, 115.344238 23.359542, 115.344238 23.359721))</t>
+    <t>114.700470 23.631499,114.700276 23.631502,114.700082 23.631326,114.699303 23.631337,114.699109 23.631161,114.698914 23.631343,114.698720 23.631346,114.698525 23.631170,114.698136 23.631176,114.698136 23.630997,114.699693 23.630973,114.699887 23.630790,114.700083 23.630788,114.700277 23.630965,114.700277 23.631144,114.700471 23.631320,114.700470 23.631499</t>
   </si>
 </sst>
 </file>
@@ -1098,8 +1077,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="1"/>
+  <cols>
+    <col min="2" max="2" width="96.3603603603604" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1175,15 +1157,15 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>20</v>
@@ -1223,15 +1205,15 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>31</v>
@@ -1261,47 +1243,10 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B20" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
